--- a/artfynd/A 18981-2025 artfynd.xlsx
+++ b/artfynd/A 18981-2025 artfynd.xlsx
@@ -2999,7 +2999,7 @@
         <v>136444082</v>
       </c>
       <c r="B22" t="n">
-        <v>56873</v>
+        <v>56875</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136444085</v>
       </c>
       <c r="B23" t="n">
-        <v>56864</v>
+        <v>56866</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>136444275</v>
       </c>
       <c r="B24" t="n">
-        <v>56864</v>
+        <v>56866</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
